--- a/ci-cd-merge-resolver/repoCollector/datasets/smart-doc.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/smart-doc.xlsx
@@ -44,6 +44,45 @@
     <t>isMultiModule</t>
   </si>
   <si>
+    <t>33203a6d72cb3f121eca95d342063c772b806a3e</t>
+  </si>
+  <si>
+    <t>723f7f87c0c36e5c3ff9dcd3ad3e725de452febf</t>
+  </si>
+  <si>
+    <t>1cd889b2f39e6a4ffc5d0cb0763ed5f30bd15157</t>
+  </si>
+  <si>
+    <t>900300dacec8ad786866ba0e91635e2c43c27217</t>
+  </si>
+  <si>
+    <t>9462fb87c1f3b9b05c2784f38012547ede3a0c67</t>
+  </si>
+  <si>
+    <t>6a3288f4ae5753285c871782c70e9266ca088b58</t>
+  </si>
+  <si>
+    <t>d1bdf37d2612c66842dc0ad03950757a2a4ae9a9</t>
+  </si>
+  <si>
+    <t>b9d108fd4b579ee1e58e1d96df07c8c25040c2cb</t>
+  </si>
+  <si>
+    <t>d073d143b6190501816d2dbf548432f72241ca63</t>
+  </si>
+  <si>
+    <t>cf6452c5d1804db57d71afc90d20328ecb3e988f</t>
+  </si>
+  <si>
+    <t>1330e887c81055ec50dd14f060b9f77511909ec6</t>
+  </si>
+  <si>
+    <t>a50b3a01cffc169e2c07a7a4566b756da160413c</t>
+  </si>
+  <si>
+    <t>4bac204e5050f303bceb0d928c48b5475aa864fb</t>
+  </si>
+  <si>
     <t>ba3c7195db6b317c5112406631fa20773c2131c9</t>
   </si>
   <si>
@@ -53,13 +92,10 @@
     <t>9cf296679eaf03e2c3c60afcf5270a51c3fc5eed</t>
   </si>
   <si>
-    <t>d1bdf37d2612c66842dc0ad03950757a2a4ae9a9</t>
-  </si>
-  <si>
-    <t>b9d108fd4b579ee1e58e1d96df07c8c25040c2cb</t>
-  </si>
-  <si>
-    <t>d073d143b6190501816d2dbf548432f72241ca63</t>
+    <t>388c178662269c58c9fa694eb702ef1bdc39f02c</t>
+  </si>
+  <si>
+    <t>31fbc383940d35ffd5e7c84657e0066cfe8a7cba</t>
   </si>
   <si>
     <t>a57687e2283d359b3b000803e6936e65a9fe20eb</t>
@@ -71,6 +107,15 @@
     <t>0ce056087bd471e4e2b704148dd4e59b2fb8da2a</t>
   </si>
   <si>
+    <t>6ad1b25c661fe8cb392ab095b3baab0c24b6b2b8</t>
+  </si>
+  <si>
+    <t>47e4b196a2e0d4ec7681f6bb882f544388453a9e</t>
+  </si>
+  <si>
+    <t>8c65ce901a27822d1c7aafeae0c267adce4da89a</t>
+  </si>
+  <si>
     <t>fbcd215aec837101c6a071dd1cba7be81ca85446</t>
   </si>
   <si>
@@ -80,16 +125,13 @@
     <t>5d99fced4547c878eb9a928aaea13a1636367180</t>
   </si>
   <si>
-    <t>33203a6d72cb3f121eca95d342063c772b806a3e</t>
-  </si>
-  <si>
-    <t>723f7f87c0c36e5c3ff9dcd3ad3e725de452febf</t>
-  </si>
-  <si>
-    <t>1cd889b2f39e6a4ffc5d0cb0763ed5f30bd15157</t>
-  </si>
-  <si>
-    <t>4bac204e5050f303bceb0d928c48b5475aa864fb</t>
+    <t>120a25f36a7f8cc3de6325b0a4886e4bd44ecd8b</t>
+  </si>
+  <si>
+    <t>d72404af10b4a7cc98a15c22bee3f819005d82fc</t>
+  </si>
+  <si>
+    <t>04850b2c686eadbb441a80ce07bc17ba55dc5986</t>
   </si>
   <si>
     <t>c3929bc003415ae0352fefd6a4bdf9ec33c68925</t>
@@ -101,15 +143,6 @@
     <t>37e4ac7090c4569b98c0dd10bb2619f09d0a989a</t>
   </si>
   <si>
-    <t>1330e887c81055ec50dd14f060b9f77511909ec6</t>
-  </si>
-  <si>
-    <t>388c178662269c58c9fa694eb702ef1bdc39f02c</t>
-  </si>
-  <si>
-    <t>31fbc383940d35ffd5e7c84657e0066cfe8a7cba</t>
-  </si>
-  <si>
     <t>95769e1519f44ccf305bcdb7ce4b6388760d8f77</t>
   </si>
   <si>
@@ -117,39 +150,6 @@
   </si>
   <si>
     <t>908fb933b86252a60fa047c688c01a711e7b4938</t>
-  </si>
-  <si>
-    <t>900300dacec8ad786866ba0e91635e2c43c27217</t>
-  </si>
-  <si>
-    <t>9462fb87c1f3b9b05c2784f38012547ede3a0c67</t>
-  </si>
-  <si>
-    <t>6a3288f4ae5753285c871782c70e9266ca088b58</t>
-  </si>
-  <si>
-    <t>cf6452c5d1804db57d71afc90d20328ecb3e988f</t>
-  </si>
-  <si>
-    <t>a50b3a01cffc169e2c07a7a4566b756da160413c</t>
-  </si>
-  <si>
-    <t>120a25f36a7f8cc3de6325b0a4886e4bd44ecd8b</t>
-  </si>
-  <si>
-    <t>d72404af10b4a7cc98a15c22bee3f819005d82fc</t>
-  </si>
-  <si>
-    <t>04850b2c686eadbb441a80ce07bc17ba55dc5986</t>
-  </si>
-  <si>
-    <t>6ad1b25c661fe8cb392ab095b3baab0c24b6b2b8</t>
-  </si>
-  <si>
-    <t>47e4b196a2e0d4ec7681f6bb882f544388453a9e</t>
-  </si>
-  <si>
-    <t>8c65ce901a27822d1c7aafeae0c267adce4da89a</t>
   </si>
   <si>
     <t>05c84dfc287aff6c746263044cd00e4c7cf6643c</t>
@@ -249,7 +249,7 @@
         <v>12</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="E2" t="n" s="0">
         <v>1.0</v>
@@ -264,7 +264,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>1.4670000076293945</v>
+        <v>0.9320000410079956</v>
       </c>
       <c r="J2" t="b" s="0">
         <v>0</v>
@@ -296,7 +296,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>4.230000019073486</v>
+        <v>5.973999977111816</v>
       </c>
       <c r="J3" t="b" s="0">
         <v>0</v>
@@ -313,7 +313,7 @@
         <v>18</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="E4" t="n" s="0">
         <v>1.0</v>
@@ -328,7 +328,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>1.319000005722046</v>
+        <v>8.293000221252441</v>
       </c>
       <c r="J4" t="b" s="0">
         <v>0</v>
@@ -345,22 +345,22 @@
         <v>21</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>14.0</v>
+        <v>10.0</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G5" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="b" s="0">
         <v>1</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>3.1969997882843018</v>
+        <v>8.875</v>
       </c>
       <c r="J5" t="b" s="0">
         <v>0</v>
@@ -371,13 +371,13 @@
         <v>22</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="E6" t="n" s="0">
         <v>1.0</v>
@@ -392,7 +392,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>3.571000099182129</v>
+        <v>8.800999641418457</v>
       </c>
       <c r="J6" t="b" s="0">
         <v>0</v>
@@ -400,13 +400,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s" s="0">
         <v>25</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="C7" t="s" s="0">
-        <v>15</v>
       </c>
       <c r="D7" t="n" s="0">
         <v>7.0</v>
@@ -424,7 +424,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="n" s="0">
-        <v>6.924000263214111</v>
+        <v>6.538000106811523</v>
       </c>
       <c r="J7" t="b" s="0">
         <v>0</v>
@@ -432,16 +432,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="B8" t="s" s="0">
+      <c r="C8" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="C8" t="s" s="0">
-        <v>28</v>
-      </c>
       <c r="D8" t="n" s="0">
-        <v>16.0</v>
+        <v>10.0</v>
       </c>
       <c r="E8" t="n" s="0">
         <v>1.0</v>
@@ -456,7 +456,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="n" s="0">
-        <v>2.5380001068115234</v>
+        <v>9.285000801086426</v>
       </c>
       <c r="J8" t="b" s="0">
         <v>0</v>
@@ -464,13 +464,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B9" t="s" s="0">
+      <c r="C9" t="s" s="0">
         <v>30</v>
-      </c>
-      <c r="C9" t="s" s="0">
-        <v>31</v>
       </c>
       <c r="D9" t="n" s="0">
         <v>7.0</v>
@@ -488,7 +488,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="n" s="0">
-        <v>6.988999843597412</v>
+        <v>4.677000045776367</v>
       </c>
       <c r="J9" t="b" s="0">
         <v>0</v>
@@ -496,31 +496,31 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B10" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="B10" t="s" s="0">
+      <c r="C10" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="C10" t="s" s="0">
-        <v>34</v>
-      </c>
       <c r="D10" t="n" s="0">
-        <v>17.0</v>
+        <v>10.0</v>
       </c>
       <c r="E10" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="F10" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G10" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="b" s="0">
         <v>1</v>
       </c>
       <c r="I10" t="n" s="0">
-        <v>6.187000274658203</v>
+        <v>5.924999713897705</v>
       </c>
       <c r="J10" t="b" s="0">
         <v>0</v>
@@ -528,22 +528,22 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B11" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="B11" t="s" s="0">
+      <c r="C11" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="C11" t="s" s="0">
-        <v>37</v>
-      </c>
       <c r="D11" t="n" s="0">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
       <c r="E11" t="n" s="0">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="F11" t="n" s="0">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G11" t="b" s="0">
         <v>0</v>
@@ -552,7 +552,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="n" s="0">
-        <v>0.1860000044107437</v>
+        <v>3.3399999141693115</v>
       </c>
       <c r="J11" t="b" s="0">
         <v>0</v>
@@ -560,22 +560,22 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B12" t="s" s="0">
         <v>38</v>
-      </c>
-      <c r="B12" t="s" s="0">
-        <v>29</v>
       </c>
       <c r="C12" t="s" s="0">
         <v>39</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="E12" t="n" s="0">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="F12" t="n" s="0">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G12" t="b" s="0">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="n" s="0">
-        <v>2.6529998779296875</v>
+        <v>5.055999755859375</v>
       </c>
       <c r="J12" t="b" s="0">
         <v>0</v>
@@ -601,13 +601,13 @@
         <v>42</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>11.0</v>
+        <v>16.0</v>
       </c>
       <c r="E13" t="n" s="0">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="F13" t="n" s="0">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G13" t="b" s="0">
         <v>0</v>
@@ -616,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="n" s="0">
-        <v>0.20400001108646393</v>
+        <v>2.9049999713897705</v>
       </c>
       <c r="J13" t="b" s="0">
         <v>0</v>
@@ -633,13 +633,13 @@
         <v>45</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="E14" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="F14" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G14" t="b" s="0">
         <v>0</v>
@@ -648,7 +648,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="n" s="0">
-        <v>0.15800000727176666</v>
+        <v>2.7129998207092285</v>
       </c>
       <c r="J14" t="b" s="0">
         <v>0</v>
@@ -665,7 +665,7 @@
         <v>48</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
       <c r="E15" t="n" s="0">
         <v>1.0</v>
@@ -680,7 +680,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="n" s="0">
-        <v>2.1460001468658447</v>
+        <v>6.804999828338623</v>
       </c>
       <c r="J15" t="b" s="0">
         <v>0</v>
